--- a/main/ig/StructureDefinition-dmi-bundle-request.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundle-request.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-bundle-request.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundle-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-bundle-request.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundle-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4091" uniqueCount="354">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -316,6 +316,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
@@ -339,6 +343,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.language</t>
   </si>
   <si>
@@ -381,6 +388,12 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -461,8 +474,8 @@
     <t>Only used if the bundle is a search result set. The total does not include resources such as OperationOutcome and included resources, only the total number of matching resources.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-1
-</t>
+    <t>ele-1
+bdl-1</t>
   </si>
   <si>
     <t>Bundle.link</t>
@@ -499,9 +512,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -522,6 +532,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -558,6 +578,9 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -565,6 +588,9 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -580,11 +606,8 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -633,6 +656,9 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -642,8 +668,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-2
-</t>
+    <t>ele-1
+bdl-2</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -699,8 +725,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-3
-</t>
+    <t>ele-1
+bdl-3</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -754,6 +780,9 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -781,8 +810,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-4
-</t>
+    <t>ele-1
+bdl-4</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1422,15 +1451,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -1877,16 +1906,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1897,10 +1926,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1923,16 +1952,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1982,7 +2011,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1991,16 +2020,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2011,10 +2040,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2037,16 +2066,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2072,13 +2101,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2096,7 +2125,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2105,16 +2134,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2125,10 +2154,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2151,16 +2180,16 @@
         <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2210,7 +2239,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2219,30 +2248,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2265,16 +2294,16 @@
         <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2285,47 +2314,47 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="AG8" t="s" s="2">
         <v>87</v>
       </c>
@@ -2333,30 +2362,30 @@
         <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2379,16 +2408,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2438,7 +2467,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2447,30 +2476,30 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2493,16 +2522,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2552,7 +2581,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2561,16 +2590,16 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2581,10 +2610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2607,16 +2636,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2666,7 +2695,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2675,16 +2704,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2695,10 +2724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2721,13 +2750,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2778,7 +2807,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2796,7 +2825,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2807,14 +2836,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2833,16 +2862,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2880,19 +2909,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2901,16 +2930,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2921,14 +2950,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2947,19 +2976,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3008,7 +3037,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3017,10 +3046,10 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3037,10 +3066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3063,15 +3092,17 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3120,7 +3151,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3129,16 +3160,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3149,10 +3180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3175,15 +3206,17 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3232,7 +3265,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3241,16 +3274,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3261,10 +3294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3287,13 +3320,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3332,17 +3365,17 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3351,16 +3384,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3371,10 +3404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3397,13 +3430,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3454,7 +3487,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3472,7 +3505,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3483,14 +3516,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3509,16 +3542,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3556,19 +3589,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3577,16 +3610,16 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3597,14 +3630,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3623,19 +3656,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3684,7 +3717,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3693,10 +3726,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3713,10 +3746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3742,10 +3775,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3796,7 +3829,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3808,7 +3841,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3825,10 +3858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3851,16 +3884,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3910,7 +3943,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3919,16 +3952,16 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3939,10 +3972,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3965,13 +3998,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4022,7 +4055,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4040,7 +4073,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4051,10 +4084,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4077,13 +4110,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4134,7 +4167,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4143,16 +4176,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4163,10 +4196,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4189,13 +4222,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4246,7 +4279,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4264,7 +4297,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4275,14 +4308,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4301,16 +4334,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4348,19 +4381,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4369,16 +4402,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4389,14 +4422,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4415,19 +4448,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4476,7 +4509,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4485,10 +4518,10 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4505,10 +4538,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4531,16 +4564,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4566,13 +4599,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4590,7 +4623,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4599,16 +4632,16 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4619,10 +4652,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4645,16 +4678,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4704,7 +4737,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4713,16 +4746,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4733,10 +4766,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4759,13 +4792,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4816,7 +4849,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4825,16 +4858,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4845,10 +4878,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4871,13 +4904,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4928,7 +4961,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4946,7 +4979,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4957,14 +4990,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4983,16 +5016,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5030,19 +5063,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5051,16 +5084,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5071,14 +5104,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5097,19 +5130,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5158,7 +5191,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5167,10 +5200,10 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5187,10 +5220,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5213,15 +5246,17 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5246,13 +5281,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5270,7 +5305,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5279,16 +5314,16 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5299,10 +5334,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5325,16 +5360,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5384,7 +5419,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5393,16 +5428,16 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5413,10 +5448,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5439,15 +5474,17 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5496,7 +5533,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5505,16 +5542,16 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5525,10 +5562,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5551,15 +5588,17 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5608,7 +5647,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5617,16 +5656,16 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5637,10 +5676,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5663,15 +5702,17 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5720,7 +5761,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5729,16 +5770,16 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5749,10 +5790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5775,15 +5816,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5832,7 +5875,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5841,16 +5884,16 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5861,10 +5904,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5887,13 +5930,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5944,7 +5987,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5953,16 +5996,16 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -5973,10 +6016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5999,13 +6042,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6056,7 +6099,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6074,7 +6117,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6085,14 +6128,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6111,16 +6154,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6158,19 +6201,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6179,16 +6222,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6199,14 +6242,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6225,19 +6268,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6286,7 +6329,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6295,10 +6338,10 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6315,10 +6358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6341,15 +6384,17 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6398,7 +6443,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6407,16 +6452,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6427,10 +6472,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6453,15 +6498,17 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6510,7 +6557,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6519,16 +6566,16 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6539,10 +6586,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6565,16 +6612,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6624,7 +6671,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6633,16 +6680,16 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6653,10 +6700,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6679,16 +6726,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6738,7 +6785,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6747,16 +6794,16 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6767,10 +6814,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6793,16 +6840,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6852,7 +6899,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6870,7 +6917,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6881,13 +6928,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6909,13 +6956,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6966,7 +7013,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6975,16 +7022,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -6995,10 +7042,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7021,13 +7068,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7078,7 +7125,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7096,7 +7143,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7107,14 +7154,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7133,16 +7180,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7180,19 +7227,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7201,16 +7248,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7221,14 +7268,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7247,19 +7294,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7308,7 +7355,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7317,10 +7364,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7337,10 +7384,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7366,10 +7413,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7420,7 +7467,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7432,7 +7479,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7449,10 +7496,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7475,16 +7522,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7534,7 +7581,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7543,16 +7590,16 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7563,10 +7610,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7586,16 +7633,16 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7646,7 +7693,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7661,10 +7708,10 @@
         <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7675,10 +7722,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7701,13 +7748,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7758,7 +7805,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7767,16 +7814,16 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7787,10 +7834,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7813,13 +7860,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7870,7 +7917,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7888,7 +7935,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7899,14 +7946,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7925,16 +7972,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7972,19 +8019,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7993,16 +8040,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8013,14 +8060,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8039,19 +8086,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8100,7 +8147,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8109,10 +8156,10 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8129,10 +8176,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8155,16 +8202,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8190,13 +8237,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8214,7 +8261,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8223,16 +8270,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8243,10 +8290,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8269,16 +8316,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8328,7 +8375,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8337,16 +8384,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8357,10 +8404,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8383,13 +8430,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8440,7 +8487,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8449,16 +8496,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8469,10 +8516,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8495,13 +8542,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8552,7 +8599,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8570,7 +8617,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8581,14 +8628,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8607,16 +8654,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8654,19 +8701,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8675,16 +8722,16 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8695,14 +8742,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8721,19 +8768,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8782,7 +8829,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8791,10 +8838,10 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8811,10 +8858,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8837,15 +8884,17 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8870,13 +8919,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8894,7 +8943,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8903,16 +8952,16 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -8923,10 +8972,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8949,16 +8998,16 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9008,7 +9057,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9017,16 +9066,16 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9037,10 +9086,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9063,15 +9112,17 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9120,7 +9171,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9129,16 +9180,16 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9149,10 +9200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9175,15 +9226,17 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9232,7 +9285,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9241,16 +9294,16 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9261,10 +9314,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9287,15 +9340,17 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9344,7 +9399,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9353,16 +9408,16 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9373,10 +9428,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9399,15 +9454,17 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9456,7 +9513,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9465,16 +9522,16 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9485,10 +9542,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9511,13 +9568,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9568,7 +9625,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9577,16 +9634,16 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9597,10 +9654,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9623,13 +9680,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9680,7 +9737,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9698,7 +9755,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9709,14 +9766,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9735,16 +9792,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9782,19 +9839,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9803,16 +9860,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9823,14 +9880,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9849,19 +9906,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9910,7 +9967,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -9919,10 +9976,10 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -9939,10 +9996,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9965,15 +10022,17 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10022,7 +10081,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10031,16 +10090,16 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10051,10 +10110,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10077,15 +10136,17 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10134,7 +10195,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10143,16 +10204,16 @@
         <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10163,10 +10224,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10189,16 +10250,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10248,7 +10309,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10257,16 +10318,16 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10277,10 +10338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10303,16 +10364,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10362,7 +10423,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10371,16 +10432,16 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -10391,10 +10452,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10417,16 +10478,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10476,7 +10537,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10494,7 +10555,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10505,13 +10566,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10533,13 +10594,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10590,7 +10651,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10599,16 +10660,16 @@
         <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -10619,10 +10680,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10645,13 +10706,13 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10702,7 +10763,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -10720,7 +10781,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -10731,14 +10792,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10757,16 +10818,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10804,19 +10865,19 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -10825,16 +10886,16 @@
         <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -10845,14 +10906,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10871,19 +10932,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -10932,7 +10993,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -10941,10 +11002,10 @@
         <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -10961,10 +11022,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10990,10 +11051,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11044,7 +11105,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11056,7 +11117,7 @@
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
@@ -11073,10 +11134,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11099,16 +11160,16 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11158,7 +11219,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11167,16 +11228,16 @@
         <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -11187,10 +11248,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11210,16 +11271,16 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11270,7 +11331,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11285,10 +11346,10 @@
         <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11299,10 +11360,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11325,13 +11386,13 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11382,7 +11443,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11391,16 +11452,16 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -11411,10 +11472,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11437,13 +11498,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11494,7 +11555,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11512,7 +11573,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11523,14 +11584,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11549,16 +11610,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11596,19 +11657,19 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11617,16 +11678,16 @@
         <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11637,14 +11698,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11663,19 +11724,19 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11724,7 +11785,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -11733,10 +11794,10 @@
         <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -11753,10 +11814,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11779,16 +11840,16 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11814,13 +11875,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -11838,7 +11899,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -11847,16 +11908,16 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -11867,10 +11928,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11893,16 +11954,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11952,7 +12013,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -11961,16 +12022,16 @@
         <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -11981,10 +12042,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12007,13 +12068,13 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12064,7 +12125,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12073,16 +12134,16 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -12093,10 +12154,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12119,13 +12180,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12176,7 +12237,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12194,7 +12255,7 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -12205,14 +12266,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12231,16 +12292,16 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12278,19 +12339,19 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12299,16 +12360,16 @@
         <v>79</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12319,14 +12380,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12345,19 +12406,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -12406,7 +12467,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12415,10 +12476,10 @@
         <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
@@ -12435,10 +12496,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12461,15 +12522,17 @@
         <v>88</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -12494,13 +12557,13 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -12518,7 +12581,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12527,16 +12590,16 @@
         <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
@@ -12547,10 +12610,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12573,16 +12636,16 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12632,7 +12695,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12641,16 +12704,16 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
@@ -12661,10 +12724,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12687,15 +12750,17 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -12744,7 +12809,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -12753,16 +12818,16 @@
         <v>87</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -12773,10 +12838,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12799,15 +12864,17 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -12856,7 +12923,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -12865,16 +12932,16 @@
         <v>87</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
@@ -12885,10 +12952,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12911,15 +12978,17 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -12968,7 +13037,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -12977,16 +13046,16 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -12997,10 +13066,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13023,15 +13092,17 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13080,7 +13151,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13089,16 +13160,16 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
@@ -13109,10 +13180,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13135,13 +13206,13 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13192,7 +13263,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13201,16 +13272,16 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -13221,10 +13292,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13247,13 +13318,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13304,7 +13375,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -13322,7 +13393,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13333,14 +13404,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13359,16 +13430,16 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13406,19 +13477,19 @@
         <v>77</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13427,16 +13498,16 @@
         <v>79</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
@@ -13447,14 +13518,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13473,19 +13544,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -13534,7 +13605,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -13543,10 +13614,10 @@
         <v>79</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>77</v>
@@ -13563,10 +13634,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13589,15 +13660,17 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -13646,7 +13719,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13655,16 +13728,16 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
@@ -13675,10 +13748,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13701,15 +13774,17 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -13758,7 +13833,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -13767,16 +13842,16 @@
         <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
@@ -13787,10 +13862,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13813,16 +13888,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13872,7 +13947,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -13881,16 +13956,16 @@
         <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
@@ -13901,10 +13976,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13927,16 +14002,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -13986,7 +14061,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -13995,16 +14070,16 @@
         <v>87</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
@@ -14015,10 +14090,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14041,16 +14116,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14100,7 +14175,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14118,7 +14193,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14129,10 +14204,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14155,19 +14230,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -14216,7 +14291,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14225,16 +14300,16 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-bundle-request.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundle-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4091" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="345">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
-bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
+    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -316,10 +316,6 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
@@ -343,9 +339,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.language</t>
   </si>
   <si>
@@ -388,12 +381,6 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -474,8 +461,8 @@
     <t>Only used if the bundle is a search result set. The total does not include resources such as OperationOutcome and included resources, only the total number of matching resources.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-1</t>
+    <t xml:space="preserve">bdl-1
+</t>
   </si>
   <si>
     <t>Bundle.link</t>
@@ -512,6 +499,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -532,16 +522,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -578,9 +558,6 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -588,9 +565,6 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -606,8 +580,11 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
+    <t>open</t>
+  </si>
+  <si>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -656,9 +633,6 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -668,8 +642,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-2</t>
+    <t xml:space="preserve">bdl-2
+</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -725,8 +699,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-3</t>
+    <t xml:space="preserve">bdl-3
+</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -780,9 +754,6 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -810,8 +781,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-4</t>
+    <t xml:space="preserve">bdl-4
+</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1451,15 +1422,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -1906,16 +1877,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1926,10 +1897,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1952,16 +1923,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2011,7 +1982,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2020,16 +1991,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2040,10 +2011,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2066,16 +2037,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2101,32 +2072,32 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Z6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>116</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2134,16 +2105,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2154,10 +2125,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2180,16 +2151,16 @@
         <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2239,7 +2210,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2248,30 +2219,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK7" t="s" s="2">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2294,16 +2265,16 @@
         <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2314,78 +2285,78 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2408,16 +2379,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2467,7 +2438,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2476,30 +2447,30 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ9" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2522,16 +2493,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2581,7 +2552,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2590,16 +2561,16 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2610,10 +2581,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2636,16 +2607,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2695,7 +2666,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2704,16 +2675,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2724,10 +2695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2750,13 +2721,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2807,7 +2778,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2825,7 +2796,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2836,14 +2807,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2862,16 +2833,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2909,19 +2880,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2930,16 +2901,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2950,14 +2921,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2976,19 +2947,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3037,7 +3008,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3046,10 +3017,10 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3066,10 +3037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3092,17 +3063,15 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3151,7 +3120,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3160,16 +3129,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3180,10 +3149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3206,17 +3175,15 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3265,7 +3232,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3274,16 +3241,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3294,10 +3261,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3320,13 +3287,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3365,17 +3332,17 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3384,16 +3351,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3404,10 +3371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3430,13 +3397,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3487,7 +3454,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3505,7 +3472,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3516,14 +3483,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3542,16 +3509,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3589,19 +3556,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3610,16 +3577,16 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3630,14 +3597,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3656,19 +3623,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O20" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3717,7 +3684,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3726,10 +3693,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3746,10 +3713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3775,10 +3742,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3829,7 +3796,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3841,7 +3808,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3858,10 +3825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3884,16 +3851,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3943,7 +3910,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3952,16 +3919,16 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3972,10 +3939,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3998,13 +3965,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4055,7 +4022,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4073,7 +4040,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4084,10 +4051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4110,13 +4077,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4167,7 +4134,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4176,16 +4143,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4196,10 +4163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4222,13 +4189,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4279,7 +4246,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4297,7 +4264,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4308,14 +4275,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4334,16 +4301,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4381,19 +4348,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4402,16 +4369,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4422,14 +4389,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4448,19 +4415,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O27" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4509,7 +4476,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4518,10 +4485,10 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4538,10 +4505,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4564,16 +4531,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4599,13 +4566,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4623,7 +4590,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4632,16 +4599,16 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4652,10 +4619,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4678,16 +4645,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4737,7 +4704,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4746,16 +4713,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4766,10 +4733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4792,13 +4759,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4849,7 +4816,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4858,16 +4825,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4878,10 +4845,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4904,13 +4871,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4961,7 +4928,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4979,7 +4946,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4990,14 +4957,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5016,16 +4983,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5063,19 +5030,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5084,16 +5051,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5104,14 +5071,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5130,19 +5097,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O33" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5191,7 +5158,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5200,10 +5167,10 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5220,10 +5187,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5246,17 +5213,15 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5281,13 +5246,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5305,7 +5270,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5314,16 +5279,16 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5334,10 +5299,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5360,16 +5325,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5419,7 +5384,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5428,16 +5393,16 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5448,10 +5413,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5474,17 +5439,15 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5533,7 +5496,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5542,16 +5505,16 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5562,10 +5525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5588,17 +5551,15 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5647,7 +5608,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5656,16 +5617,16 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5676,10 +5637,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5702,17 +5663,15 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5761,7 +5720,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5770,16 +5729,16 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5790,10 +5749,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5816,17 +5775,15 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5875,7 +5832,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5884,16 +5841,16 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5904,10 +5861,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5930,13 +5887,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5987,7 +5944,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5996,16 +5953,16 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6016,10 +5973,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6042,13 +5999,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6099,7 +6056,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6117,7 +6074,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6128,14 +6085,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6154,16 +6111,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6201,19 +6158,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6222,16 +6179,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6242,14 +6199,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6268,19 +6225,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O43" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6329,7 +6286,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6338,10 +6295,10 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6358,10 +6315,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6384,17 +6341,15 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6443,7 +6398,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6452,16 +6407,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6472,10 +6427,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6498,17 +6453,15 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6557,7 +6510,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6566,16 +6519,16 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6586,10 +6539,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6612,16 +6565,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6671,7 +6624,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6680,16 +6633,16 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6700,10 +6653,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6726,16 +6679,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6785,7 +6738,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6794,16 +6747,16 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6814,10 +6767,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6840,16 +6793,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6899,7 +6852,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6917,7 +6870,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6928,13 +6881,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6956,13 +6909,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7013,7 +6966,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7022,16 +6975,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7042,10 +6995,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7068,13 +7021,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7125,7 +7078,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7143,7 +7096,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7154,14 +7107,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7180,16 +7133,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7227,19 +7180,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7248,16 +7201,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7268,14 +7221,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7294,19 +7247,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7355,7 +7308,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7364,10 +7317,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7384,10 +7337,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7413,10 +7366,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7467,7 +7420,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7479,7 +7432,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7496,10 +7449,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7522,16 +7475,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7581,7 +7534,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7590,16 +7543,16 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ54" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7610,10 +7563,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7633,16 +7586,16 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7693,7 +7646,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7708,10 +7661,10 @@
         <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7722,10 +7675,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7748,13 +7701,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7805,7 +7758,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7814,16 +7767,16 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7834,10 +7787,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7860,13 +7813,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7917,7 +7870,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7935,7 +7888,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7946,14 +7899,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7972,16 +7925,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8019,19 +7972,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8040,16 +7993,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8060,14 +8013,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8086,19 +8039,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8147,7 +8100,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8156,10 +8109,10 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8176,10 +8129,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8202,16 +8155,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8237,13 +8190,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8261,7 +8214,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8270,16 +8223,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8290,10 +8243,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8316,16 +8269,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8375,7 +8328,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8384,16 +8337,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8404,10 +8357,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8430,13 +8383,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8487,7 +8440,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8496,16 +8449,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8516,10 +8469,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8542,13 +8495,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8599,7 +8552,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8617,7 +8570,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8628,14 +8581,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8654,16 +8607,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8701,19 +8654,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8722,16 +8675,16 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8742,14 +8695,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8768,19 +8721,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O65" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8829,7 +8782,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8838,10 +8791,10 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8858,10 +8811,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8884,17 +8837,15 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8919,13 +8870,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8943,7 +8894,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8952,16 +8903,16 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -8972,10 +8923,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8998,16 +8949,16 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9057,7 +9008,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9066,16 +9017,16 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ67" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9086,10 +9037,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9112,17 +9063,15 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9171,7 +9120,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9180,16 +9129,16 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9200,10 +9149,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9226,17 +9175,15 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9285,7 +9232,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9294,16 +9241,16 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ69" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9314,10 +9261,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9340,17 +9287,15 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9399,7 +9344,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9408,16 +9353,16 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ70" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9428,10 +9373,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9454,17 +9399,15 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9513,7 +9456,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9522,16 +9465,16 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ71" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9542,10 +9485,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9568,13 +9511,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9625,7 +9568,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9634,16 +9577,16 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9654,10 +9597,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9680,13 +9623,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9737,7 +9680,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9755,7 +9698,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9766,14 +9709,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9792,16 +9735,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9839,19 +9782,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9860,16 +9803,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9880,14 +9823,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9906,19 +9849,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9967,7 +9910,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -9976,10 +9919,10 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -9996,10 +9939,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10022,17 +9965,15 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10081,7 +10022,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10090,16 +10031,16 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ76" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10110,10 +10051,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10136,17 +10077,15 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10195,7 +10134,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10204,16 +10143,16 @@
         <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ77" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10224,10 +10163,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10250,16 +10189,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10309,7 +10248,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10318,16 +10257,16 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ78" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10338,10 +10277,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10364,16 +10303,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10423,7 +10362,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10432,16 +10371,16 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ79" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -10452,10 +10391,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10478,16 +10417,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10537,7 +10476,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10555,7 +10494,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10566,13 +10505,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10594,13 +10533,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10651,7 +10590,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10660,16 +10599,16 @@
         <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -10680,10 +10619,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10706,13 +10645,13 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10763,7 +10702,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -10781,7 +10720,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -10792,14 +10731,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10818,16 +10757,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10865,19 +10804,19 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -10886,16 +10825,16 @@
         <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -10906,14 +10845,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10932,19 +10871,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L84" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -10993,7 +10932,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11002,10 +10941,10 @@
         <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -11022,10 +10961,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11051,10 +10990,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11105,7 +11044,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11117,7 +11056,7 @@
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
@@ -11134,10 +11073,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11160,16 +11099,16 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11219,7 +11158,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11228,16 +11167,16 @@
         <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ86" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -11248,10 +11187,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11271,16 +11210,16 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11331,7 +11270,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11346,10 +11285,10 @@
         <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11360,10 +11299,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11386,13 +11325,13 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11443,7 +11382,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11452,16 +11391,16 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -11472,10 +11411,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11498,13 +11437,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11555,7 +11494,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11573,7 +11512,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11584,14 +11523,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11610,16 +11549,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11657,19 +11596,19 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11678,16 +11617,16 @@
         <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11698,14 +11637,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11724,19 +11663,19 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L91" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11785,7 +11724,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -11794,10 +11733,10 @@
         <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -11814,10 +11753,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11840,16 +11779,16 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11875,13 +11814,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -11899,7 +11838,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -11908,16 +11847,16 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ92" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -11928,10 +11867,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11954,16 +11893,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12013,7 +11952,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12022,16 +11961,16 @@
         <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ93" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -12042,10 +11981,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12068,13 +12007,13 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12125,7 +12064,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12134,16 +12073,16 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -12154,10 +12093,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12180,13 +12119,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12237,7 +12176,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12255,7 +12194,7 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -12266,14 +12205,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12292,16 +12231,16 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12339,19 +12278,19 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12360,16 +12299,16 @@
         <v>79</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12380,14 +12319,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12406,19 +12345,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L97" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -12467,7 +12406,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12476,10 +12415,10 @@
         <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
@@ -12496,10 +12435,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12522,17 +12461,15 @@
         <v>88</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -12557,13 +12494,13 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -12581,7 +12518,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12590,16 +12527,16 @@
         <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ98" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
@@ -12610,10 +12547,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12636,16 +12573,16 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12695,7 +12632,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12704,16 +12641,16 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ99" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
@@ -12724,10 +12661,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12750,17 +12687,15 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -12809,7 +12744,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -12818,16 +12753,16 @@
         <v>87</v>
       </c>
       <c r="AI100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ100" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -12838,10 +12773,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12864,17 +12799,15 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -12923,7 +12856,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -12932,16 +12865,16 @@
         <v>87</v>
       </c>
       <c r="AI101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ101" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
@@ -12952,10 +12885,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12978,17 +12911,15 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -13037,7 +12968,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13046,16 +12977,16 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ102" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -13066,10 +12997,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13092,17 +13023,15 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13151,7 +13080,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13160,16 +13089,16 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ103" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
@@ -13180,10 +13109,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13206,13 +13135,13 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13263,7 +13192,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13272,16 +13201,16 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -13292,10 +13221,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13318,13 +13247,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13375,7 +13304,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -13393,7 +13322,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13404,14 +13333,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13430,16 +13359,16 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13477,19 +13406,19 @@
         <v>77</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13498,16 +13427,16 @@
         <v>79</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
@@ -13518,14 +13447,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13544,19 +13473,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L107" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O107" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -13605,7 +13534,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -13614,10 +13543,10 @@
         <v>79</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>77</v>
@@ -13634,10 +13563,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13660,17 +13589,15 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -13719,7 +13646,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13728,16 +13655,16 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ108" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
@@ -13748,10 +13675,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13774,17 +13701,15 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -13833,7 +13758,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -13842,16 +13767,16 @@
         <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ109" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
@@ -13862,10 +13787,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13888,16 +13813,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13947,7 +13872,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -13956,16 +13881,16 @@
         <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ110" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
@@ -13976,10 +13901,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14002,16 +13927,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14061,7 +13986,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14070,16 +13995,16 @@
         <v>87</v>
       </c>
       <c r="AI111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ111" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
@@ -14090,10 +14015,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14116,16 +14041,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14175,7 +14100,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14193,7 +14118,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14204,10 +14129,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14230,19 +14155,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -14291,7 +14216,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14300,16 +14225,16 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ113" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-bundle-request.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundle-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-bundle-request.xlsx
+++ b/main/ig/StructureDefinition-dmi-bundle-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4091" uniqueCount="354">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -316,6 +316,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
@@ -339,6 +343,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.language</t>
   </si>
   <si>
@@ -381,6 +388,12 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -461,8 +474,8 @@
     <t>Only used if the bundle is a search result set. The total does not include resources such as OperationOutcome and included resources, only the total number of matching resources.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-1
-</t>
+    <t>ele-1
+bdl-1</t>
   </si>
   <si>
     <t>Bundle.link</t>
@@ -499,9 +512,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -522,6 +532,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -558,6 +578,9 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -565,6 +588,9 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -580,11 +606,8 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -633,6 +656,9 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -642,8 +668,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-2
-</t>
+    <t>ele-1
+bdl-2</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -699,8 +725,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-3
-</t>
+    <t>ele-1
+bdl-3</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -754,6 +780,9 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -781,8 +810,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-4
-</t>
+    <t>ele-1
+bdl-4</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1422,15 +1451,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -1877,16 +1906,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1897,10 +1926,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1923,16 +1952,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1982,7 +2011,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1991,16 +2020,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2011,10 +2040,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2037,16 +2066,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2072,13 +2101,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2096,7 +2125,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2105,16 +2134,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2125,10 +2154,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2151,16 +2180,16 @@
         <v>88</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2210,7 +2239,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2219,30 +2248,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2265,16 +2294,16 @@
         <v>88</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2285,47 +2314,47 @@
         <v>77</v>
       </c>
       <c r="S8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>122</v>
-      </c>
       <c r="AG8" t="s" s="2">
         <v>87</v>
       </c>
@@ -2333,30 +2362,30 @@
         <v>87</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2379,16 +2408,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2438,7 +2467,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2447,30 +2476,30 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2493,16 +2522,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2552,7 +2581,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2561,16 +2590,16 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2581,10 +2610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2607,16 +2636,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2666,7 +2695,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2675,16 +2704,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2695,10 +2724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2721,13 +2750,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2778,7 +2807,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2796,7 +2825,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2807,14 +2836,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2833,16 +2862,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2880,19 +2909,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2901,16 +2930,16 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2921,14 +2950,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2947,19 +2976,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3008,7 +3037,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3017,10 +3046,10 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3037,10 +3066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3063,15 +3092,17 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3120,7 +3151,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3129,16 +3160,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3149,10 +3180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3175,15 +3206,17 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3232,7 +3265,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3241,16 +3274,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3261,10 +3294,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3287,13 +3320,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3332,17 +3365,17 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3351,16 +3384,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3371,10 +3404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3397,13 +3430,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3454,7 +3487,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3472,7 +3505,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3483,14 +3516,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3509,16 +3542,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3556,19 +3589,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3577,16 +3610,16 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3597,14 +3630,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3623,19 +3656,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3684,7 +3717,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3693,10 +3726,10 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3713,10 +3746,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3742,10 +3775,10 @@
         <v>80</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3796,7 +3829,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3808,7 +3841,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3825,10 +3858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3851,16 +3884,16 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3910,7 +3943,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3919,16 +3952,16 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -3939,10 +3972,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3965,13 +3998,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4022,7 +4055,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4040,7 +4073,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4051,10 +4084,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4077,13 +4110,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4134,7 +4167,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4143,16 +4176,16 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4163,10 +4196,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4189,13 +4222,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4246,7 +4279,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4264,7 +4297,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4275,14 +4308,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4301,16 +4334,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4348,19 +4381,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4369,16 +4402,16 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4389,14 +4422,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4415,19 +4448,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4476,7 +4509,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4485,10 +4518,10 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4505,10 +4538,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4531,16 +4564,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4566,13 +4599,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4590,7 +4623,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4599,16 +4632,16 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4619,10 +4652,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4645,16 +4678,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4704,7 +4737,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4713,16 +4746,16 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4733,10 +4766,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4759,13 +4792,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4816,7 +4849,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4825,16 +4858,16 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4845,10 +4878,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4871,13 +4904,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4928,7 +4961,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4946,7 +4979,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4957,14 +4990,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4983,16 +5016,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5030,19 +5063,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5051,16 +5084,16 @@
         <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5071,14 +5104,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5097,19 +5130,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5158,7 +5191,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5167,10 +5200,10 @@
         <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5187,10 +5220,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5213,15 +5246,17 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5246,13 +5281,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5270,7 +5305,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5279,16 +5314,16 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5299,10 +5334,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5325,16 +5360,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5384,7 +5419,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5393,16 +5428,16 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5413,10 +5448,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5439,15 +5474,17 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5496,7 +5533,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5505,16 +5542,16 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5525,10 +5562,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5551,15 +5588,17 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5608,7 +5647,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5617,16 +5656,16 @@
         <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5637,10 +5676,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5663,15 +5702,17 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5720,7 +5761,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5729,16 +5770,16 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5749,10 +5790,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5775,15 +5816,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5832,7 +5875,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5841,16 +5884,16 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -5861,10 +5904,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5887,13 +5930,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5944,7 +5987,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5953,16 +5996,16 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -5973,10 +6016,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5999,13 +6042,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6056,7 +6099,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6074,7 +6117,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6085,14 +6128,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6111,16 +6154,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6158,19 +6201,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6179,16 +6222,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6199,14 +6242,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6225,19 +6268,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6286,7 +6329,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6295,10 +6338,10 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6315,10 +6358,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6341,15 +6384,17 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6398,7 +6443,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6407,16 +6452,16 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6427,10 +6472,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6453,15 +6498,17 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6510,7 +6557,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6519,16 +6566,16 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6539,10 +6586,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6565,16 +6612,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6624,7 +6671,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6633,16 +6680,16 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6653,10 +6700,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6679,16 +6726,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6738,7 +6785,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6747,16 +6794,16 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6767,10 +6814,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6793,16 +6840,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6852,7 +6899,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6870,7 +6917,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6881,13 +6928,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6909,13 +6956,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6966,7 +7013,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6975,16 +7022,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -6995,10 +7042,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7021,13 +7068,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7078,7 +7125,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7096,7 +7143,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7107,14 +7154,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7133,16 +7180,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7180,19 +7227,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7201,16 +7248,16 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7221,14 +7268,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7247,19 +7294,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7308,7 +7355,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7317,10 +7364,10 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7337,10 +7384,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7366,10 +7413,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7420,7 +7467,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7432,7 +7479,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7449,10 +7496,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7475,16 +7522,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7534,7 +7581,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7543,16 +7590,16 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7563,10 +7610,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7586,16 +7633,16 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7646,7 +7693,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7661,10 +7708,10 @@
         <v>77</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7675,10 +7722,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7701,13 +7748,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7758,7 +7805,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7767,16 +7814,16 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7787,10 +7834,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7813,13 +7860,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7870,7 +7917,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7888,7 +7935,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7899,14 +7946,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7925,16 +7972,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7972,19 +8019,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -7993,16 +8040,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8013,14 +8060,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8039,19 +8086,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8100,7 +8147,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8109,10 +8156,10 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8129,10 +8176,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8155,16 +8202,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8190,13 +8237,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8214,7 +8261,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8223,16 +8270,16 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8243,10 +8290,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8269,16 +8316,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8328,7 +8375,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8337,16 +8384,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8357,10 +8404,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8383,13 +8430,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8440,7 +8487,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8449,16 +8496,16 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8469,10 +8516,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8495,13 +8542,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8552,7 +8599,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8570,7 +8617,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8581,14 +8628,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8607,16 +8654,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8654,19 +8701,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8675,16 +8722,16 @@
         <v>79</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8695,14 +8742,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8721,19 +8768,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8782,7 +8829,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8791,10 +8838,10 @@
         <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8811,10 +8858,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8837,15 +8884,17 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -8870,13 +8919,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8894,7 +8943,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8903,16 +8952,16 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -8923,10 +8972,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8949,16 +8998,16 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9008,7 +9057,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9017,16 +9066,16 @@
         <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9037,10 +9086,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9063,15 +9112,17 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9120,7 +9171,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9129,16 +9180,16 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -9149,10 +9200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9175,15 +9226,17 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9232,7 +9285,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9241,16 +9294,16 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9261,10 +9314,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9287,15 +9340,17 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9344,7 +9399,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9353,16 +9408,16 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9373,10 +9428,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9399,15 +9454,17 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9456,7 +9513,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9465,16 +9522,16 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9485,10 +9542,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9511,13 +9568,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9568,7 +9625,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9577,16 +9634,16 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9597,10 +9654,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9623,13 +9680,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9680,7 +9737,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9698,7 +9755,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9709,14 +9766,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9735,16 +9792,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9782,19 +9839,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9803,16 +9860,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9823,14 +9880,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9849,19 +9906,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9910,7 +9967,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -9919,10 +9976,10 @@
         <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -9939,10 +9996,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9965,15 +10022,17 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10022,7 +10081,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10031,16 +10090,16 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -10051,10 +10110,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10077,15 +10136,17 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10134,7 +10195,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10143,16 +10204,16 @@
         <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -10163,10 +10224,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10189,16 +10250,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10248,7 +10309,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10257,16 +10318,16 @@
         <v>87</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -10277,10 +10338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10303,16 +10364,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10362,7 +10423,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10371,16 +10432,16 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -10391,10 +10452,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10417,16 +10478,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10476,7 +10537,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10494,7 +10555,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10505,13 +10566,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10533,13 +10594,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10590,7 +10651,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10599,16 +10660,16 @@
         <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -10619,10 +10680,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10645,13 +10706,13 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10702,7 +10763,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -10720,7 +10781,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -10731,14 +10792,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10757,16 +10818,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10804,19 +10865,19 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -10825,16 +10886,16 @@
         <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -10845,14 +10906,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10871,19 +10932,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -10932,7 +10993,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -10941,10 +11002,10 @@
         <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -10961,10 +11022,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10990,10 +11051,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11044,7 +11105,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11056,7 +11117,7 @@
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
@@ -11073,10 +11134,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11099,16 +11160,16 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11158,7 +11219,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11167,16 +11228,16 @@
         <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -11187,10 +11248,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11210,16 +11271,16 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11270,7 +11331,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11285,10 +11346,10 @@
         <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11299,10 +11360,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11325,13 +11386,13 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11382,7 +11443,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11391,16 +11452,16 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -11411,10 +11472,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11437,13 +11498,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11494,7 +11555,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11512,7 +11573,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11523,14 +11584,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11549,16 +11610,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11596,19 +11657,19 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11617,16 +11678,16 @@
         <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11637,14 +11698,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11663,19 +11724,19 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11724,7 +11785,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -11733,10 +11794,10 @@
         <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -11753,10 +11814,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11779,16 +11840,16 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11814,13 +11875,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -11838,7 +11899,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -11847,16 +11908,16 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -11867,10 +11928,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11893,16 +11954,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11952,7 +12013,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -11961,16 +12022,16 @@
         <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -11981,10 +12042,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12007,13 +12068,13 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12064,7 +12125,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12073,16 +12134,16 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -12093,10 +12154,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12119,13 +12180,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12176,7 +12237,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12194,7 +12255,7 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -12205,14 +12266,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12231,16 +12292,16 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12278,19 +12339,19 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12299,16 +12360,16 @@
         <v>79</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12319,14 +12380,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12345,19 +12406,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -12406,7 +12467,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12415,10 +12476,10 @@
         <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
@@ -12435,10 +12496,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12461,15 +12522,17 @@
         <v>88</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -12494,13 +12557,13 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -12518,7 +12581,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12527,16 +12590,16 @@
         <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
@@ -12547,10 +12610,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12573,16 +12636,16 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12632,7 +12695,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12641,16 +12704,16 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
@@ -12661,10 +12724,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12687,15 +12750,17 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -12744,7 +12809,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -12753,16 +12818,16 @@
         <v>87</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -12773,10 +12838,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12799,15 +12864,17 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -12856,7 +12923,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -12865,16 +12932,16 @@
         <v>87</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
@@ -12885,10 +12952,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12911,15 +12978,17 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -12968,7 +13037,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -12977,16 +13046,16 @@
         <v>87</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -12997,10 +13066,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13023,15 +13092,17 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13080,7 +13151,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13089,16 +13160,16 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
@@ -13109,10 +13180,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13135,13 +13206,13 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13192,7 +13263,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13201,16 +13272,16 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -13221,10 +13292,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13247,13 +13318,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13304,7 +13375,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -13322,7 +13393,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13333,14 +13404,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13359,16 +13430,16 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13406,19 +13477,19 @@
         <v>77</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13427,16 +13498,16 @@
         <v>79</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
@@ -13447,14 +13518,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13473,19 +13544,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -13534,7 +13605,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -13543,10 +13614,10 @@
         <v>79</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>77</v>
@@ -13563,10 +13634,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13589,15 +13660,17 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -13646,7 +13719,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13655,16 +13728,16 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
@@ -13675,10 +13748,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13701,15 +13774,17 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -13758,7 +13833,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -13767,16 +13842,16 @@
         <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
@@ -13787,10 +13862,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13813,16 +13888,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13872,7 +13947,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -13881,16 +13956,16 @@
         <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
@@ -13901,10 +13976,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13927,16 +14002,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -13986,7 +14061,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -13995,16 +14070,16 @@
         <v>87</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
@@ -14015,10 +14090,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14041,16 +14116,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14100,7 +14175,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14118,7 +14193,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14129,10 +14204,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14155,19 +14230,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -14216,7 +14291,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14225,16 +14300,16 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
